--- a/Data/Input/Config.xlsx
+++ b/Data/Input/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BOT-DEV-012\Documents\UiPath\Email_To_Case_Latest\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD18D24-DC31-4163-BE94-79BBFEA17823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B73D04-DBC2-404B-8AE6-48EC30EB1EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="157">
   <si>
     <t>Name</t>
   </si>
@@ -408,9 +408,6 @@
     <t>BioAg US</t>
   </si>
   <si>
-    <t xml:space="preserve">BioAgCS@novozymes.com </t>
-  </si>
-  <si>
     <t>Brazil Mailbox</t>
   </si>
   <si>
@@ -505,6 +502,12 @@
   </si>
   <si>
     <t xml:space="preserve">Order@novozymes.com </t>
+  </si>
+  <si>
+    <t>BioAgCS@novozymes.com</t>
+  </si>
+  <si>
+    <t>SIBI@novozymes.com;vsk@novozymes.com</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1053,7 @@
         <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
@@ -2166,7 +2169,7 @@
       <c r="C2" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="6" t="s">
         <v>119</v>
       </c>
       <c r="E2" s="12" t="s">
@@ -2183,7 +2186,7 @@
       <c r="C3" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>121</v>
       </c>
       <c r="E3" s="12" t="s">
@@ -2200,8 +2203,8 @@
       <c r="C4" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>123</v>
+      <c r="D4" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>120</v>
@@ -2209,13 +2212,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>117</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>121</v>
@@ -2226,13 +2229,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>117</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>121</v>
@@ -2243,206 +2246,206 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="C7" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="D7" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="E7" s="12" t="s">
         <v>131</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>135</v>
-      </c>
       <c r="E8" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>134</v>
-      </c>
       <c r="D9" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="C11" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>139</v>
-      </c>
       <c r="E11" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="C12" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="D12" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>143</v>
-      </c>
       <c r="E12" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>141</v>
-      </c>
       <c r="C13" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>145</v>
-      </c>
       <c r="E13" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>141</v>
-      </c>
       <c r="C14" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>147</v>
-      </c>
       <c r="E14" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>141</v>
-      </c>
       <c r="C15" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>149</v>
-      </c>
       <c r="E15" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>141</v>
-      </c>
       <c r="C16" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>151</v>
-      </c>
       <c r="E16" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="12" t="s">
+      <c r="D17" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>154</v>
-      </c>
       <c r="E17" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>141</v>
-      </c>
       <c r="C18" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
